--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/94.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/94.xlsx
@@ -426,13 +426,13 @@
         <v>-18.10552345012104</v>
       </c>
       <c r="E2">
-        <v>-8.865160160875462</v>
+        <v>-9.747990697144806</v>
       </c>
       <c r="F2">
-        <v>-1.030710504474504</v>
+        <v>-1.698304312362933</v>
       </c>
       <c r="G2">
-        <v>-10.57090411211516</v>
+        <v>-12.68610766297616</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.84313434476062</v>
       </c>
       <c r="E3">
-        <v>-10.16795684814215</v>
+        <v>-10.23753685127</v>
       </c>
       <c r="F3">
-        <v>-1.154029724844985</v>
+        <v>-1.367171993621445</v>
       </c>
       <c r="G3">
-        <v>-10.62366758692007</v>
+        <v>-11.4833831580134</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.32359730003109</v>
       </c>
       <c r="E4">
-        <v>-10.00886702777868</v>
+        <v>-11.49083278915884</v>
       </c>
       <c r="F4">
-        <v>-1.285067927847318</v>
+        <v>-1.327219844492654</v>
       </c>
       <c r="G4">
-        <v>-9.288713272027735</v>
+        <v>-11.50079662754997</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.74899352849689</v>
       </c>
       <c r="E5">
-        <v>-11.71780443489729</v>
+        <v>-12.44590154279854</v>
       </c>
       <c r="F5">
-        <v>-1.094100709298841</v>
+        <v>-1.156237410891108</v>
       </c>
       <c r="G5">
-        <v>-9.619887005594267</v>
+        <v>-10.09245413914307</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.13523354541615</v>
       </c>
       <c r="E6">
-        <v>-12.03522329199093</v>
+        <v>-11.97279374932119</v>
       </c>
       <c r="F6">
-        <v>-0.9227318514539268</v>
+        <v>-1.40440016857568</v>
       </c>
       <c r="G6">
-        <v>-9.024051708890699</v>
+        <v>-10.11494929608242</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.53854905383888</v>
       </c>
       <c r="E7">
-        <v>-12.27121112947865</v>
+        <v>-13.34979854015157</v>
       </c>
       <c r="F7">
-        <v>-0.878439556263874</v>
+        <v>-1.023939369833042</v>
       </c>
       <c r="G7">
-        <v>-8.289491311909511</v>
+        <v>-10.20571121258708</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.95932019171287</v>
       </c>
       <c r="E8">
-        <v>-13.51727509437724</v>
+        <v>-14.22354948603554</v>
       </c>
       <c r="F8">
-        <v>-0.9038429910004805</v>
+        <v>-1.462989368917363</v>
       </c>
       <c r="G8">
-        <v>-9.12534116021024</v>
+        <v>-8.762058445458317</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.400083829819129</v>
       </c>
       <c r="E9">
-        <v>-13.8831123955609</v>
+        <v>-14.56558059936087</v>
       </c>
       <c r="F9">
-        <v>-0.965285237548827</v>
+        <v>-1.333833400395529</v>
       </c>
       <c r="G9">
-        <v>-7.309308299187638</v>
+        <v>-8.352646589162187</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.853044451098784</v>
       </c>
       <c r="E10">
-        <v>-14.20769529853468</v>
+        <v>-14.74771129547536</v>
       </c>
       <c r="F10">
-        <v>-0.668217641195484</v>
+        <v>-0.8892412224601287</v>
       </c>
       <c r="G10">
-        <v>-7.088521396082564</v>
+        <v>-7.680238374135278</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.322189248033308</v>
       </c>
       <c r="E11">
-        <v>-15.97604628463393</v>
+        <v>-17.08331704967143</v>
       </c>
       <c r="F11">
-        <v>-0.7532499792072588</v>
+        <v>-0.948186756632785</v>
       </c>
       <c r="G11">
-        <v>-5.97301983444298</v>
+        <v>-6.725294960604808</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.816452106067372</v>
       </c>
       <c r="E12">
-        <v>-16.30410252717159</v>
+        <v>-17.12146491471204</v>
       </c>
       <c r="F12">
-        <v>-0.5051315652883184</v>
+        <v>-1.016311450291328</v>
       </c>
       <c r="G12">
-        <v>-5.851681719337613</v>
+        <v>-6.028143728217385</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.352072643327138</v>
       </c>
       <c r="E13">
-        <v>-15.77598735992306</v>
+        <v>-17.67851703086958</v>
       </c>
       <c r="F13">
-        <v>-0.2242470678318934</v>
+        <v>-1.110461975111246</v>
       </c>
       <c r="G13">
-        <v>-5.229415027048504</v>
+        <v>-5.850969952046669</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.04363351084614386</v>
       </c>
       <c r="E14">
-        <v>-18.33551256837641</v>
+        <v>-19.44384752480571</v>
       </c>
       <c r="F14">
-        <v>-0.6527060336067123</v>
+        <v>-0.7672554824704476</v>
       </c>
       <c r="G14">
-        <v>-4.778068490406428</v>
+        <v>-4.67844424349314</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.344466153518253</v>
       </c>
       <c r="E15">
-        <v>-19.49864658877253</v>
+        <v>-19.36895562166686</v>
       </c>
       <c r="F15">
-        <v>-0.07037736849962753</v>
+        <v>-0.9181422717109832</v>
       </c>
       <c r="G15">
-        <v>-3.765574553221267</v>
+        <v>-3.677229334960276</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.522588778427874</v>
       </c>
       <c r="E16">
-        <v>-18.59496242969786</v>
+        <v>-20.47909743922522</v>
       </c>
       <c r="F16">
-        <v>0.04686517227331247</v>
+        <v>-0.7350231078264662</v>
       </c>
       <c r="G16">
-        <v>-3.61438855953383</v>
+        <v>-3.690008040741863</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.550295314487556</v>
       </c>
       <c r="E17">
-        <v>-21.30258685209805</v>
+        <v>-21.90277721165266</v>
       </c>
       <c r="F17">
-        <v>-0.01934165352163362</v>
+        <v>-0.684324722208461</v>
       </c>
       <c r="G17">
-        <v>-3.809637914348967</v>
+        <v>-2.551660404335769</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.391542171053535</v>
       </c>
       <c r="E18">
-        <v>-21.14630015714533</v>
+        <v>-22.90545834100901</v>
       </c>
       <c r="F18">
-        <v>0.02691206144469088</v>
+        <v>-0.371283076139038</v>
       </c>
       <c r="G18">
-        <v>-2.660441620210681</v>
+        <v>-3.360486269399427</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.012966600854211</v>
       </c>
       <c r="E19">
-        <v>-22.59959162110893</v>
+        <v>-22.62323025542897</v>
       </c>
       <c r="F19">
-        <v>0.098676111296914</v>
+        <v>-0.4397799406877095</v>
       </c>
       <c r="G19">
-        <v>-2.023214572629606</v>
+        <v>-2.77913791997571</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.387668940664959</v>
       </c>
       <c r="E20">
-        <v>-22.68569602589077</v>
+        <v>-23.51553888779636</v>
       </c>
       <c r="F20">
-        <v>0.2724260709856912</v>
+        <v>-0.2455954235720171</v>
       </c>
       <c r="G20">
-        <v>-1.619771629940783</v>
+        <v>-1.446226211681109</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.505158630036405</v>
       </c>
       <c r="E21">
-        <v>-22.99807016293987</v>
+        <v>-23.24724038826392</v>
       </c>
       <c r="F21">
-        <v>0.4190891165497498</v>
+        <v>0.08426517931937275</v>
       </c>
       <c r="G21">
-        <v>-1.489935344436107</v>
+        <v>-1.609515559860121</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.36868408972646</v>
       </c>
       <c r="E22">
-        <v>-23.83741376331356</v>
+        <v>-24.46204429708756</v>
       </c>
       <c r="F22">
-        <v>0.7628111054660235</v>
+        <v>0.2938615305511642</v>
       </c>
       <c r="G22">
-        <v>-1.585865022527568</v>
+        <v>-1.667082636242508</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.001742892043895</v>
       </c>
       <c r="E23">
-        <v>-25.37805496241111</v>
+        <v>-25.00696463137855</v>
       </c>
       <c r="F23">
-        <v>0.3287268162795636</v>
+        <v>-0.01035253874559932</v>
       </c>
       <c r="G23">
-        <v>-1.142308199539396</v>
+        <v>-2.072349689523469</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.445260753954248</v>
       </c>
       <c r="E24">
-        <v>-23.89461744697845</v>
+        <v>-26.38786843832953</v>
       </c>
       <c r="F24">
-        <v>0.3881910141395262</v>
+        <v>-0.207327545684296</v>
       </c>
       <c r="G24">
-        <v>-1.701671216036813</v>
+        <v>-2.268085694532878</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.75380561502523</v>
       </c>
       <c r="E25">
-        <v>-23.68853112336338</v>
+        <v>-25.55098832781602</v>
       </c>
       <c r="F25">
-        <v>0.3867276698736602</v>
+        <v>0.1983078422901673</v>
       </c>
       <c r="G25">
-        <v>-1.323825411457636</v>
+        <v>-2.818907503538975</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.985949690756728</v>
       </c>
       <c r="E26">
-        <v>-24.53026122953911</v>
+        <v>-25.88316095322666</v>
       </c>
       <c r="F26">
-        <v>0.7462692971792585</v>
+        <v>-0.7230946348713763</v>
       </c>
       <c r="G26">
-        <v>-2.137987875930599</v>
+        <v>-2.20457287836196</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.200236703364144</v>
       </c>
       <c r="E27">
-        <v>-25.01916886882922</v>
+        <v>-24.9078680346687</v>
       </c>
       <c r="F27">
-        <v>0.5355152569232808</v>
+        <v>-0.4233711636978414</v>
       </c>
       <c r="G27">
-        <v>-1.836999696591141</v>
+        <v>-2.559076026343736</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.447736082672776</v>
       </c>
       <c r="E28">
-        <v>-24.16258989638234</v>
+        <v>-24.98947566476093</v>
       </c>
       <c r="F28">
-        <v>0.5328182057492874</v>
+        <v>-0.412331149761313</v>
       </c>
       <c r="G28">
-        <v>-1.472654296721111</v>
+        <v>-3.023664745142898</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.7666793758428964</v>
       </c>
       <c r="E29">
-        <v>-23.78445778826786</v>
+        <v>-25.50047320026046</v>
       </c>
       <c r="F29">
-        <v>0.358229673778285</v>
+        <v>-0.006070989803208774</v>
       </c>
       <c r="G29">
-        <v>-2.004135898686786</v>
+        <v>-1.640757178114223</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.1836593671202749</v>
       </c>
       <c r="E30">
-        <v>-23.86620580105433</v>
+        <v>-24.99230143254172</v>
       </c>
       <c r="F30">
-        <v>0.5385963567817683</v>
+        <v>-0.2248623375800416</v>
       </c>
       <c r="G30">
-        <v>-1.722646832573635</v>
+        <v>-2.789648902062896</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.2883377849686355</v>
       </c>
       <c r="E31">
-        <v>-23.25229416525648</v>
+        <v>-25.27224716722189</v>
       </c>
       <c r="F31">
-        <v>0.4238932884442354</v>
+        <v>-0.5407388172381011</v>
       </c>
       <c r="G31">
-        <v>-1.568815713000321</v>
+        <v>-2.346015936527321</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.6487063420546926</v>
       </c>
       <c r="E32">
-        <v>-24.37200917686706</v>
+        <v>-25.01037457230633</v>
       </c>
       <c r="F32">
-        <v>0.3533019728223952</v>
+        <v>-0.2533318269689388</v>
       </c>
       <c r="G32">
-        <v>-1.905604131801458</v>
+        <v>-2.242356134601662</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.9092055576534248</v>
       </c>
       <c r="E33">
-        <v>-22.23526230176983</v>
+        <v>-24.23513604998522</v>
       </c>
       <c r="F33">
-        <v>0.2101230802723034</v>
+        <v>-0.3562434129130673</v>
       </c>
       <c r="G33">
-        <v>-1.905567715800526</v>
+        <v>-1.45358224386937</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.087705947103077</v>
       </c>
       <c r="E34">
-        <v>-22.44925081252828</v>
+        <v>-23.37940390217778</v>
       </c>
       <c r="F34">
-        <v>0.230107073366276</v>
+        <v>-0.3809872341358932</v>
       </c>
       <c r="G34">
-        <v>-2.178873113340598</v>
+        <v>-2.458706906684113</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.209955199854637</v>
       </c>
       <c r="E35">
-        <v>-21.91394442855557</v>
+        <v>-23.31940615005015</v>
       </c>
       <c r="F35">
-        <v>-0.04551081006835505</v>
+        <v>-0.4317101671955878</v>
       </c>
       <c r="G35">
-        <v>-2.055538739275049</v>
+        <v>-2.762598434461511</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.302359673327282</v>
       </c>
       <c r="E36">
-        <v>-21.0521758248959</v>
+        <v>-22.94804411057714</v>
       </c>
       <c r="F36">
-        <v>-0.0375716923142571</v>
+        <v>-0.04582834310440066</v>
       </c>
       <c r="G36">
-        <v>-1.37558910150968</v>
+        <v>-2.046411565223279</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.388549918824116</v>
       </c>
       <c r="E37">
-        <v>-21.10169015969577</v>
+        <v>-22.50879571725514</v>
       </c>
       <c r="F37">
-        <v>0.2435654062356804</v>
+        <v>-0.2198902928585194</v>
       </c>
       <c r="G37">
-        <v>-1.501618259644194</v>
+        <v>-2.27102545897175</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.487380664673103</v>
       </c>
       <c r="E38">
-        <v>-19.99923769100243</v>
+        <v>-21.55027173794758</v>
       </c>
       <c r="F38">
-        <v>0.3614145063742338</v>
+        <v>-0.5601186265253336</v>
       </c>
       <c r="G38">
-        <v>-1.995770150109047</v>
+        <v>-3.103955406106842</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.612837201735756</v>
       </c>
       <c r="E39">
-        <v>-19.61256488090948</v>
+        <v>-22.11221913450741</v>
       </c>
       <c r="F39">
-        <v>0.3582407597196931</v>
+        <v>-0.1313088698902448</v>
       </c>
       <c r="G39">
-        <v>-1.897135756312002</v>
+        <v>-2.060398620126699</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.773221888870536</v>
       </c>
       <c r="E40">
-        <v>-18.91047932770829</v>
+        <v>-20.54301232136948</v>
       </c>
       <c r="F40">
-        <v>0.4609852646897427</v>
+        <v>-0.1128373159455168</v>
       </c>
       <c r="G40">
-        <v>-2.658269902336919</v>
+        <v>-3.15752003293225</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.970295704109988</v>
       </c>
       <c r="E41">
-        <v>-18.50155359634164</v>
+        <v>-20.84734388858096</v>
       </c>
       <c r="F41">
-        <v>0.3948148641308517</v>
+        <v>-0.005930039976734663</v>
       </c>
       <c r="G41">
-        <v>-1.866185466065355</v>
+        <v>-2.732323495504876</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.202523203702535</v>
       </c>
       <c r="E42">
-        <v>-18.62035358345887</v>
+        <v>-19.96829462810802</v>
       </c>
       <c r="F42">
-        <v>0.5440292599246833</v>
+        <v>0.03969652744707582</v>
       </c>
       <c r="G42">
-        <v>-2.421234841725102</v>
+        <v>-2.360519436534868</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.467202139439357</v>
       </c>
       <c r="E43">
-        <v>-17.97307615117251</v>
+        <v>-18.68113476158982</v>
       </c>
       <c r="F43">
-        <v>0.8543984022618022</v>
+        <v>-0.3981862803775656</v>
       </c>
       <c r="G43">
-        <v>-3.350938656064169</v>
+        <v>-4.081192033298764</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.760302713282719</v>
       </c>
       <c r="E44">
-        <v>-17.01999992609618</v>
+        <v>-18.55553300651308</v>
       </c>
       <c r="F44">
-        <v>0.3556514005479496</v>
+        <v>0.05027093184446501</v>
       </c>
       <c r="G44">
-        <v>-2.713304411381763</v>
+        <v>-3.579856259013693</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.076856768272963</v>
       </c>
       <c r="E45">
-        <v>-16.57356031605</v>
+        <v>-17.5122178798859</v>
       </c>
       <c r="F45">
-        <v>0.3711012436060191</v>
+        <v>-0.2214922113919864</v>
       </c>
       <c r="G45">
-        <v>-3.986288624324477</v>
+        <v>-3.819890673884089</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.414113059289159</v>
       </c>
       <c r="E46">
-        <v>-15.84801726748907</v>
+        <v>-17.80502900922187</v>
       </c>
       <c r="F46">
-        <v>0.2942368688531233</v>
+        <v>0.533587886824191</v>
       </c>
       <c r="G46">
-        <v>-3.604496649462488</v>
+        <v>-4.770196013114041</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.772299587893679</v>
       </c>
       <c r="E47">
-        <v>-15.22311502527461</v>
+        <v>-16.31152469607016</v>
       </c>
       <c r="F47">
-        <v>0.7667006871943428</v>
+        <v>-0.268203617367873</v>
       </c>
       <c r="G47">
-        <v>-3.673792988690513</v>
+        <v>-4.953557198897654</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.152835719147617</v>
       </c>
       <c r="E48">
-        <v>-14.69168954352647</v>
+        <v>-16.30248133347684</v>
       </c>
       <c r="F48">
-        <v>0.8703637415953472</v>
+        <v>0.1525189450100243</v>
       </c>
       <c r="G48">
-        <v>-3.776992624786213</v>
+        <v>-5.195624288729163</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.557800856835869</v>
       </c>
       <c r="E49">
-        <v>-14.09050291969018</v>
+        <v>-15.12036395004056</v>
       </c>
       <c r="F49">
-        <v>1.047471157824856</v>
+        <v>0.5098639722109081</v>
       </c>
       <c r="G49">
-        <v>-3.852827291454298</v>
+        <v>-5.35362007459088</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.99312185034962</v>
       </c>
       <c r="E50">
-        <v>-13.15412770675414</v>
+        <v>-14.45718704551327</v>
       </c>
       <c r="F50">
-        <v>0.4845840665357059</v>
+        <v>0.1893797001918775</v>
       </c>
       <c r="G50">
-        <v>-4.327562832331326</v>
+        <v>-5.522481070912486</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.462233046277638</v>
       </c>
       <c r="E51">
-        <v>-13.33090574659157</v>
+        <v>-14.19674544838413</v>
       </c>
       <c r="F51">
-        <v>0.5424043776554425</v>
+        <v>0.3554114691017605</v>
       </c>
       <c r="G51">
-        <v>-5.063060113700127</v>
+        <v>-5.531065315495816</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.963919540094716</v>
       </c>
       <c r="E52">
-        <v>-12.4098639466455</v>
+        <v>-13.80774953112525</v>
       </c>
       <c r="F52">
-        <v>0.598927633630434</v>
+        <v>0.3226311322110371</v>
       </c>
       <c r="G52">
-        <v>-4.575714704864016</v>
+        <v>-5.107567087930089</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.492375153507266</v>
       </c>
       <c r="E53">
-        <v>-12.36348331585894</v>
+        <v>-13.97447435866565</v>
       </c>
       <c r="F53">
-        <v>0.3545317204657339</v>
+        <v>0.2975515653341381</v>
       </c>
       <c r="G53">
-        <v>-5.123825177073449</v>
+        <v>-5.935316031296221</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.040669992640971</v>
       </c>
       <c r="E54">
-        <v>-11.94473079589566</v>
+        <v>-12.91232078016657</v>
       </c>
       <c r="F54">
-        <v>0.508683319450948</v>
+        <v>0.367188698141926</v>
       </c>
       <c r="G54">
-        <v>-5.034718533338427</v>
+        <v>-6.561936090969471</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.602360386203164</v>
       </c>
       <c r="E55">
-        <v>-11.34425514247857</v>
+        <v>-12.05999404481289</v>
       </c>
       <c r="F55">
-        <v>0.4717227907964222</v>
+        <v>0.319659308060715</v>
       </c>
       <c r="G55">
-        <v>-5.634821123242115</v>
+        <v>-6.405327423688709</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.16665543197314</v>
       </c>
       <c r="E56">
-        <v>-11.2830528162649</v>
+        <v>-11.12277653571143</v>
       </c>
       <c r="F56">
-        <v>0.5802652431228955</v>
+        <v>-0.07632814347689126</v>
       </c>
       <c r="G56">
-        <v>-6.130714360660624</v>
+        <v>-6.332018703267087</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.721208864830164</v>
       </c>
       <c r="E57">
-        <v>-10.39080758253361</v>
+        <v>-12.08822455177671</v>
       </c>
       <c r="F57">
-        <v>0.9091518668762901</v>
+        <v>0.058091271654905</v>
       </c>
       <c r="G57">
-        <v>-5.666589118236961</v>
+        <v>-6.434569472437091</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.254902445679342</v>
       </c>
       <c r="E58">
-        <v>-10.07685300805583</v>
+        <v>-10.71466140119216</v>
       </c>
       <c r="F58">
-        <v>0.4411968592763268</v>
+        <v>-0.08821623193113748</v>
       </c>
       <c r="G58">
-        <v>-6.236867003377355</v>
+        <v>-6.309480509235729</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.765416368883695</v>
       </c>
       <c r="E59">
-        <v>-10.8430345823616</v>
+        <v>-10.761209585517</v>
       </c>
       <c r="F59">
-        <v>0.6762029800683864</v>
+        <v>0.2942986333838254</v>
       </c>
       <c r="G59">
-        <v>-6.507951024860576</v>
+        <v>-7.819287907875746</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.24623331226704</v>
       </c>
       <c r="E60">
-        <v>-9.755335881985246</v>
+        <v>-10.12898480083214</v>
       </c>
       <c r="F60">
-        <v>0.2565676318014383</v>
+        <v>0.07558092793206053</v>
       </c>
       <c r="G60">
-        <v>-6.293278699366536</v>
+        <v>-7.672696951396818</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.69041517319164</v>
       </c>
       <c r="E61">
-        <v>-9.487829865404144</v>
+        <v>-10.42757426300189</v>
       </c>
       <c r="F61">
-        <v>0.5424740607157218</v>
+        <v>0.1063650035163725</v>
       </c>
       <c r="G61">
-        <v>-6.860623441159135</v>
+        <v>-7.32906232442047</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.09209431582346</v>
       </c>
       <c r="E62">
-        <v>-9.816923128489563</v>
+        <v>-10.00636278165244</v>
       </c>
       <c r="F62">
-        <v>0.5577069360633761</v>
+        <v>-0.1510933160388721</v>
       </c>
       <c r="G62">
-        <v>-7.2357115613041</v>
+        <v>-7.192280514374402</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.44771629602461</v>
       </c>
       <c r="E63">
-        <v>-9.271894110822391</v>
+        <v>-10.92521280017879</v>
       </c>
       <c r="F63">
-        <v>0.5020151256939902</v>
+        <v>-0.4073709828341567</v>
       </c>
       <c r="G63">
-        <v>-6.805290983015757</v>
+        <v>-7.453128329050196</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.75071525777852</v>
       </c>
       <c r="E64">
-        <v>-9.918143579509012</v>
+        <v>-7.05610272192127</v>
       </c>
       <c r="F64">
-        <v>0.1012361719092219</v>
+        <v>-0.07659578977660053</v>
       </c>
       <c r="G64">
-        <v>-7.203258283382625</v>
+        <v>-7.807469260300548</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.99325288358645</v>
       </c>
       <c r="E65">
-        <v>-8.779662571610645</v>
+        <v>-9.052752196643207</v>
       </c>
       <c r="F65">
-        <v>0.1738894726329642</v>
+        <v>-0.3907539485164083</v>
       </c>
       <c r="G65">
-        <v>-7.455588064385875</v>
+        <v>-8.412961418342171</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.16958951508706</v>
       </c>
       <c r="E66">
-        <v>-8.758066279068066</v>
+        <v>-8.902923105625424</v>
       </c>
       <c r="F66">
-        <v>0.01583720597802282</v>
+        <v>-0.0001629748856619149</v>
       </c>
       <c r="G66">
-        <v>-7.182481299578159</v>
+        <v>-8.101144444543756</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.28069897176615</v>
       </c>
       <c r="E67">
-        <v>-8.284424125657807</v>
+        <v>-8.484691360173022</v>
       </c>
       <c r="F67">
-        <v>0.4389907569361197</v>
+        <v>-0.06670871374651205</v>
       </c>
       <c r="G67">
-        <v>-6.810346186054224</v>
+        <v>-8.238601605879834</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.32567306069312</v>
       </c>
       <c r="E68">
-        <v>-7.864996863067379</v>
+        <v>-7.750652894373703</v>
       </c>
       <c r="F68">
-        <v>0.1983830683211507</v>
+        <v>-0.5578190855361156</v>
       </c>
       <c r="G68">
-        <v>-8.021078900676482</v>
+        <v>-8.577515394917183</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.30424651003099</v>
       </c>
       <c r="E69">
-        <v>-8.902895934781379</v>
+        <v>-9.459925408568878</v>
       </c>
       <c r="F69">
-        <v>-0.03057725513871878</v>
+        <v>-0.4773351509134829</v>
       </c>
       <c r="G69">
-        <v>-7.567371945064906</v>
+        <v>-8.623508804094278</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.21890816520658</v>
       </c>
       <c r="E70">
-        <v>-9.104503597602863</v>
+        <v>-9.19062158780673</v>
       </c>
       <c r="F70">
-        <v>-0.1040604177621514</v>
+        <v>-1.005535123389721</v>
       </c>
       <c r="G70">
-        <v>-7.805923235533709</v>
+        <v>-8.409902474263884</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.08101843016974</v>
       </c>
       <c r="E71">
-        <v>-8.467424288781775</v>
+        <v>-10.06854325825176</v>
       </c>
       <c r="F71">
-        <v>-0.1456770418080692</v>
+        <v>-0.2078762997839958</v>
       </c>
       <c r="G71">
-        <v>-7.543575743728624</v>
+        <v>-8.989476371278551</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.89892038984447</v>
       </c>
       <c r="E72">
-        <v>-9.56069301218756</v>
+        <v>-8.625318592007217</v>
       </c>
       <c r="F72">
-        <v>-0.2066821855237544</v>
+        <v>-0.747615945413083</v>
       </c>
       <c r="G72">
-        <v>-7.946949164961122</v>
+        <v>-8.180925281494652</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.67955957440184</v>
       </c>
       <c r="E73">
-        <v>-9.033334100098315</v>
+        <v>-8.694350649780144</v>
       </c>
       <c r="F73">
-        <v>-0.003107084182463848</v>
+        <v>-0.5013275036794328</v>
       </c>
       <c r="G73">
-        <v>-7.662980500239057</v>
+        <v>-9.153040494737322</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.42961865199643</v>
       </c>
       <c r="E74">
-        <v>-9.532326651003512</v>
+        <v>-9.892154667178991</v>
       </c>
       <c r="F74">
-        <v>-0.2751529189248212</v>
+        <v>-0.5062813357829273</v>
       </c>
       <c r="G74">
-        <v>-8.299889735448362</v>
+        <v>-8.996941651469607</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.16280099199297</v>
       </c>
       <c r="E75">
-        <v>-9.387986070483027</v>
+        <v>-9.340971453335394</v>
       </c>
       <c r="F75">
-        <v>-0.194407672826141</v>
+        <v>-0.6293827965900356</v>
       </c>
       <c r="G75">
-        <v>-7.678351363177893</v>
+        <v>-7.426213593815921</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.88738319356962</v>
       </c>
       <c r="E76">
-        <v>-9.304503652151624</v>
+        <v>-10.27480619235313</v>
       </c>
       <c r="F76">
-        <v>-0.4250182178498985</v>
+        <v>-1.183893667292427</v>
       </c>
       <c r="G76">
-        <v>-7.225551497044077</v>
+        <v>-7.976631516266227</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.6086495414345</v>
       </c>
       <c r="E77">
-        <v>-10.421143829911</v>
+        <v>-10.20274458546907</v>
       </c>
       <c r="F77">
-        <v>-0.4230631328972884</v>
+        <v>-0.6700769119402099</v>
       </c>
       <c r="G77">
-        <v>-7.508954058478926</v>
+        <v>-8.075980987899756</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.32911461269655</v>
       </c>
       <c r="E78">
-        <v>-9.704684900209454</v>
+        <v>-11.43942555222377</v>
       </c>
       <c r="F78">
-        <v>-0.03398143100395588</v>
+        <v>-1.098034634792792</v>
       </c>
       <c r="G78">
-        <v>-7.177677698000676</v>
+        <v>-8.387890656973269</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.05691805484136</v>
       </c>
       <c r="E79">
-        <v>-10.52849130626282</v>
+        <v>-10.63818000367661</v>
       </c>
       <c r="F79">
-        <v>-0.4546279754979121</v>
+        <v>-0.7081721658831481</v>
       </c>
       <c r="G79">
-        <v>-7.872346021233646</v>
+        <v>-7.960277421302228</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.793133611853937</v>
       </c>
       <c r="E80">
-        <v>-11.62573150137333</v>
+        <v>-10.81618525997012</v>
       </c>
       <c r="F80">
-        <v>-0.1999894443251073</v>
+        <v>-0.4850470068687153</v>
       </c>
       <c r="G80">
-        <v>-7.188142332450313</v>
+        <v>-8.236462993461465</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.534012810534595</v>
       </c>
       <c r="E81">
-        <v>-13.56467463181553</v>
+        <v>-12.40527207400173</v>
       </c>
       <c r="F81">
-        <v>-0.3419140417901712</v>
+        <v>-1.048537490111648</v>
       </c>
       <c r="G81">
-        <v>-7.014249306909015</v>
+        <v>-8.090656636275344</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.271664549564196</v>
       </c>
       <c r="E82">
-        <v>-13.17484094686523</v>
+        <v>-13.12534472596139</v>
       </c>
       <c r="F82">
-        <v>-0.4712307564624215</v>
+        <v>-0.8895262895249079</v>
       </c>
       <c r="G82">
-        <v>-6.68585643159547</v>
+        <v>-7.728098930996522</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.004240072257883</v>
       </c>
       <c r="E83">
-        <v>-13.42052877567737</v>
+        <v>-13.23830298160872</v>
       </c>
       <c r="F83">
-        <v>-0.08884892244435554</v>
+        <v>-1.074363774327677</v>
       </c>
       <c r="G83">
-        <v>-6.809144458023469</v>
+        <v>-6.659686569107532</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.726279400593594</v>
       </c>
       <c r="E84">
-        <v>-13.89321994954602</v>
+        <v>-13.57566070975814</v>
       </c>
       <c r="F84">
-        <v>-0.05767129594005685</v>
+        <v>-0.8204030692866801</v>
       </c>
       <c r="G84">
-        <v>-6.761949320815618</v>
+        <v>-7.431378044857184</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.433465085597023</v>
       </c>
       <c r="E85">
-        <v>-16.30088731062614</v>
+        <v>-15.38546081844959</v>
       </c>
       <c r="F85">
-        <v>-0.4863662338962763</v>
+        <v>-1.080044527446358</v>
       </c>
       <c r="G85">
-        <v>-7.236890115516081</v>
+        <v>-7.728102241542061</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.122740718766581</v>
       </c>
       <c r="E86">
-        <v>-16.65956962287768</v>
+        <v>-15.29048966156073</v>
       </c>
       <c r="F86">
-        <v>-0.3826382475527388</v>
+        <v>-1.122518728245486</v>
       </c>
       <c r="G86">
-        <v>-6.60940931400262</v>
+        <v>-6.855733765397632</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.802226803221186</v>
       </c>
       <c r="E87">
-        <v>-18.70750859421049</v>
+        <v>-18.2989043844984</v>
       </c>
       <c r="F87">
-        <v>-0.4260207036943716</v>
+        <v>-1.229731659455948</v>
       </c>
       <c r="G87">
-        <v>-6.24710983127586</v>
+        <v>-6.239955742365495</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.478957576408914</v>
       </c>
       <c r="E88">
-        <v>-19.66869531623456</v>
+        <v>-19.34611399877217</v>
       </c>
       <c r="F88">
-        <v>-0.584550457682818</v>
+        <v>-0.8792155721624393</v>
       </c>
       <c r="G88">
-        <v>-5.742410542722888</v>
+        <v>-6.422525707765222</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.160913841349899</v>
       </c>
       <c r="E89">
-        <v>-21.52925056160398</v>
+        <v>-20.96663295089101</v>
       </c>
       <c r="F89">
-        <v>-0.4671867634073469</v>
+        <v>-0.687211818092307</v>
       </c>
       <c r="G89">
-        <v>-6.183745989654209</v>
+        <v>-6.877086784125931</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.853938669471986</v>
       </c>
       <c r="E90">
-        <v>-21.61519194132154</v>
+        <v>-22.34891341394033</v>
       </c>
       <c r="F90">
-        <v>-0.5321377104113495</v>
+        <v>-1.194158457183347</v>
       </c>
       <c r="G90">
-        <v>-5.530969309675178</v>
+        <v>-6.692146468120085</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.57023219875933</v>
       </c>
       <c r="E91">
-        <v>-24.60420215313635</v>
+        <v>-23.63131385427646</v>
       </c>
       <c r="F91">
-        <v>-0.3092849488143722</v>
+        <v>-0.9694820582247415</v>
       </c>
       <c r="G91">
-        <v>-5.856846170378876</v>
+        <v>-6.42934874212166</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.3163703012887</v>
       </c>
       <c r="E92">
-        <v>-26.46190445988094</v>
+        <v>-26.53407475014118</v>
       </c>
       <c r="F92">
-        <v>-0.4451455363292184</v>
+        <v>-1.139595037278712</v>
       </c>
       <c r="G92">
-        <v>-5.600305375449673</v>
+        <v>-5.786507009305981</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.095865933576143</v>
       </c>
       <c r="E93">
-        <v>-27.6214021156489</v>
+        <v>-28.97709590779919</v>
       </c>
       <c r="F93">
-        <v>-0.3485925296355793</v>
+        <v>-1.282550627294727</v>
       </c>
       <c r="G93">
-        <v>-5.249619286474676</v>
+        <v>-6.367239597259394</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.90663451377163</v>
       </c>
       <c r="E94">
-        <v>-30.37504489091504</v>
+        <v>-30.60510269168971</v>
       </c>
       <c r="F94">
-        <v>-0.8138766172091541</v>
+        <v>-1.159248035836358</v>
       </c>
       <c r="G94">
-        <v>-5.397448386985292</v>
+        <v>-6.273918629052878</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.75061829890473</v>
       </c>
       <c r="E95">
-        <v>-32.63607120667878</v>
+        <v>-32.43093812684232</v>
       </c>
       <c r="F95">
-        <v>-0.6047712148111489</v>
+        <v>-0.9304698385567639</v>
       </c>
       <c r="G95">
-        <v>-5.237797328353939</v>
+        <v>-6.201632867202892</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.621245499798982</v>
       </c>
       <c r="E96">
-        <v>-34.76493627276567</v>
+        <v>-34.56819898373943</v>
       </c>
       <c r="F96">
-        <v>-0.7431340576723894</v>
+        <v>-0.9480885668660277</v>
       </c>
       <c r="G96">
-        <v>-6.203970112353617</v>
+        <v>-5.486319981987027</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.509768466920636</v>
       </c>
       <c r="E97">
-        <v>-37.65466648467331</v>
+        <v>-36.29197846441818</v>
       </c>
       <c r="F97">
-        <v>-0.9520541664782881</v>
+        <v>-1.269983920855715</v>
       </c>
       <c r="G97">
-        <v>-6.100038845693738</v>
+        <v>-6.629067333414812</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.398637907854903</v>
       </c>
       <c r="E98">
-        <v>-39.57929284454025</v>
+        <v>-38.08355146522875</v>
       </c>
       <c r="F98">
-        <v>-0.8135392878491654</v>
+        <v>-1.565882742243464</v>
       </c>
       <c r="G98">
-        <v>-5.953629969219469</v>
+        <v>-7.096426978830344</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.280972402592692</v>
       </c>
       <c r="E99">
-        <v>-41.66771637350163</v>
+        <v>-42.23129175646722</v>
       </c>
       <c r="F99">
-        <v>-0.5610482618976966</v>
+        <v>-1.311439006898258</v>
       </c>
       <c r="G99">
-        <v>-6.137742648840497</v>
+        <v>-6.506289130999861</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.139607691603721</v>
       </c>
       <c r="E100">
-        <v>-44.7011599722797</v>
+        <v>-44.28147232243384</v>
       </c>
       <c r="F100">
-        <v>-0.7668278818732789</v>
+        <v>-1.353724746693449</v>
       </c>
       <c r="G100">
-        <v>-6.396422056188069</v>
+        <v>-6.867562344609448</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.974800005273881</v>
       </c>
       <c r="E101">
-        <v>-46.12882480183389</v>
+        <v>-46.29787500077722</v>
       </c>
       <c r="F101">
-        <v>-0.9400678882572846</v>
+        <v>-1.782150454644044</v>
       </c>
       <c r="G101">
-        <v>-6.050119129507067</v>
+        <v>-6.774449940771906</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.768217713753066</v>
       </c>
       <c r="E102">
-        <v>-48.80229886962373</v>
+        <v>-49.39640862070454</v>
       </c>
       <c r="F102">
-        <v>-1.007243150219522</v>
+        <v>-1.723487611977293</v>
       </c>
       <c r="G102">
-        <v>-6.811528050811744</v>
+        <v>-7.810173976006133</v>
       </c>
     </row>
   </sheetData>
